--- a/Hybrid Framework Project/OpenCardProject/testData/Opencart_LoginData.xlsx
+++ b/Hybrid Framework Project/OpenCardProject/testData/Opencart_LoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YouTube Pavan Sir Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105E0C21-ED11-42DD-8247-3C98E32BB3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85ECDC7-C502-4A63-BE1B-FCC61C1ED4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t>username</t>
   </si>
@@ -40,32 +40,23 @@
     <t>valid</t>
   </si>
   <si>
-    <t>kapil@gmail.com</t>
-  </si>
-  <si>
-    <t>invalid</t>
-  </si>
-  <si>
     <t>basef@gmail.com</t>
   </si>
   <si>
     <t>lksdjflksdj@gmail.com</t>
   </si>
   <si>
-    <t>xyz</t>
-  </si>
-  <si>
-    <t>sdlfjsdlk@gmail.com</t>
-  </si>
-  <si>
-    <t>sldkfjsd</t>
+    <t>Invalid</t>
+  </si>
+  <si>
+    <t>xyz@123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +77,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -130,7 +127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -141,6 +138,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -476,56 +474,58 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
+      <c r="C5" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{9DFD7EC9-124B-4095-BF7C-ABA19445DECA}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{1526305C-FA91-468C-9308-D880C004CE0A}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{7616ECFD-4FAE-4699-AE8B-EB2FCD626764}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{8EE4BE7B-7775-40BF-80B9-2F00A88E3330}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{2C2B913D-0434-47F4-8059-122FA45673A3}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{7616ECFD-4FAE-4699-AE8B-EB2FCD626764}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{8EE4BE7B-7775-40BF-80B9-2F00A88E3330}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{745C3A78-BB91-43D7-B99D-CED7466F3C59}"/>
+    <hyperlink ref="A3" r:id="rId5" xr:uid="{564F5B43-A98A-4E37-A158-27E2EE6E079D}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{DF9EFC06-2E85-4448-A90F-3F12F835D511}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>